--- a/docs/release/testing/staging_validation_test_cases.xlsx
+++ b/docs/release/testing/staging_validation_test_cases.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Environment &amp; Access" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment &amp; Access" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$N$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2351,13 +2351,293 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TC-DLV-01</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Demo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>S4/S5</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>An offer was accepted (TC-MRP-03 or TC-MRE-03). Delivery status is 'pending'. Logged in as buyer or seller with a @promoshake.net email.</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Open the Exchange Status screen of the accepted proposal. In the 'Demo actions (staging only)' panel, click the purple 'Pickup' button.</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Delivery status updates to 'picked_up' in real time (no manual refresh). Snackbar 'Pickup done — the courier is on the way.' A courier ID equal to the caller's uid is written on the delivery doc.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TC-DLV-02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Demo</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>S4/S5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>TC-DLV-01 (delivery in 'picked_up').</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Click the green 'Delivered' button in the demo panel.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Snackbar 'Delivered — wallet credited and inventory transferred.' Status updates to 'delivered'. Seller wallet increases by the trade totalAmount (no courier fee deducted in demo mode). Buyer's deducted balance decreases by the same amount. For exchange: buyer's item B is transferred to seller and seller's item A to buyer.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TC-DLV-03</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Demo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Delivered delivery (TC-DLV-02).</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Confirm the 'Reset delivery' button is NOT visible on a delivered delivery.</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Only a 'Delivered — nothing left to do for the demo.' line is shown; no reset button (backend would refuse because settlement already ran).</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TC-DLV-04</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Demo</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>A delivery in 'failed' or 'cancelled' status (rare - trigger via the courier UI or by canceling the proposal).</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Open the delivery card; click the orange 'Reset delivery' button.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Status returns to 'pending', courierId + pickedUpAt cleared. Demo can be replayed.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-DLV-05</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Delivery - Demo</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Not logged in as buyer or seller of the delivery (a third pharmacy).</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Somehow reach the Exchange Status screen and click a demo button.</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Backend refuses with 'permission-denied' (only the two trade parties can drive the demo).</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N38"/>
   <dataValidations count="2">
-    <dataValidation sqref="J2:J33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"-,Critical,Major,Minor"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2410,7 +2690,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2902,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2632,7 +2912,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Cases'!J2:J33,"Pass")</f>
+        <f>COUNTIF('Test Cases'!J2:J38,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -2643,7 +2923,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Cases'!J2:J33,"Fail")</f>
+        <f>COUNTIF('Test Cases'!J2:J38,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -2654,7 +2934,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Cases'!J2:J33,"Blocked")</f>
+        <f>COUNTIF('Test Cases'!J2:J38,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -2665,7 +2945,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF('Test Cases'!J2:J33,"Not Run")</f>
+        <f>COUNTIF('Test Cases'!J2:J38,"Not Run")</f>
         <v/>
       </c>
     </row>
